--- a/전화번호/독산_전화번호없는기사목록.xlsx
+++ b/전화번호/독산_전화번호없는기사목록.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="102">
   <si>
     <t>박성순</t>
   </si>
@@ -270,9 +270,6 @@
     <t xml:space="preserve">김승범 예비독산 </t>
   </si>
   <si>
-    <t>driver_name</t>
-  </si>
-  <si>
     <t>tel_number</t>
   </si>
   <si>
@@ -288,8 +285,45 @@
     <t>car_number</t>
   </si>
   <si>
-    <t>ds.driver_name</t>
+    <t>01075321175</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tel_section</t>
+  </si>
+  <si>
+    <t>cell</t>
+  </si>
+  <si>
+    <t>cell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fn_front</t>
+  </si>
+  <si>
+    <t>fn_new</t>
+  </si>
+  <si>
+    <t>fn_order</t>
+  </si>
+  <si>
+    <t>fn_order 에 들어갈목록 정의</t>
+  </si>
+  <si>
+    <t>고정/쉬프트</t>
+  </si>
+  <si>
+    <t>박원호</t>
+  </si>
+  <si>
+    <t>차현철</t>
+  </si>
+  <si>
+    <t>진영만</t>
+  </si>
+  <si>
+    <t>한원석</t>
   </si>
 </sst>
 </file>
@@ -313,12 +347,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -335,8 +375,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -633,589 +694,735 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.296875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" t="s">
         <v>86</v>
       </c>
-      <c r="D1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>87</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>2</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
+        <v>41</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" t="s">
+        <v>41</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>41</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" t="s">
+        <v>41</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" s="7"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" t="s">
-        <v>2</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" t="s">
-        <v>2</v>
-      </c>
-      <c r="F24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" t="s">
-        <v>2</v>
-      </c>
-      <c r="F26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" t="s">
-        <v>2</v>
-      </c>
-      <c r="F28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29" t="s">
-        <v>2</v>
-      </c>
-      <c r="F29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" t="s">
-        <v>69</v>
-      </c>
-      <c r="E30" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" t="s">
-        <v>2</v>
-      </c>
-      <c r="F31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>72</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>73</v>
       </c>
-      <c r="E32" t="s">
-        <v>2</v>
-      </c>
-      <c r="F32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" t="s">
+      <c r="F32" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" t="s">
         <v>74</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>75</v>
       </c>
-      <c r="E33" t="s">
-        <v>2</v>
-      </c>
-      <c r="F33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" t="s">
+      <c r="G33" t="s">
+        <v>2</v>
+      </c>
+      <c r="H33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" t="s">
         <v>76</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>77</v>
       </c>
-      <c r="E34" t="s">
-        <v>2</v>
-      </c>
-      <c r="F34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" t="s">
+      <c r="G34" t="s">
+        <v>2</v>
+      </c>
+      <c r="H34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" t="s">
         <v>78</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>79</v>
       </c>
-      <c r="E35" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" t="s">
+      <c r="G35" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" t="s">
         <v>80</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>81</v>
       </c>
-      <c r="E36" t="s">
-        <v>2</v>
-      </c>
-      <c r="F36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" t="s">
+      <c r="G36" t="s">
+        <v>2</v>
+      </c>
+      <c r="H36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
         <v>82</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>83</v>
       </c>
-      <c r="E37" t="s">
-        <v>2</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
+        <v>2</v>
+      </c>
+      <c r="H37" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F37">
+      <formula1>$J$18:$J$22</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
